--- a/templates/000_pm_suite/01_프로젝트 관리/02_범위관리/프로젝트명_산출물목록_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/01_프로젝트 관리/02_범위관리/프로젝트명_산출물목록_V1.0_20230530.xlsx
@@ -846,7 +846,7 @@
     <t>준공30일 전</t>
   </si>
   <si>
-    <t>ⓒ 엠파시인터네셔널. All rights reserved.</t>
+    <t>ⓒ 주식회사 엠파시 (Empasy Inc.). All rights reserved.</t>
   </si>
   <si>
     <t>설명</t>

--- a/templates/000_pm_suite/01_프로젝트 관리/02_범위관리/프로젝트명_산출물목록_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/01_프로젝트 관리/02_범위관리/프로젝트명_산출물목록_V1.0_20230530.xlsx
@@ -533,7 +533,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-09] SyncGuard AI 단계별 표준 산출물 목록 및 테일러링 정의서 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-09] SyncFlow AI 단계별 표준 산출물 목록 및 테일러링 정의서 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>규제심의팀 / IT정보화팀</t>
+          <t>규제검증팀 / IT정보화팀</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>규제심의팀 / IT정보화팀</t>
+          <t>규제검증팀 / IT정보화팀</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀 / 마케팅팀</t>
+          <t>규제검증팀 / 구매조달팀</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀 / IT정보화팀</t>
+          <t>규제검증팀 / IT정보화팀</t>
         </is>
       </c>
     </row>
